--- a/Document/操作方法/拡張機能など.xlsx
+++ b/Document/操作方法/拡張機能など.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\操作方法\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE0C76-A672-42D6-B020-323D1C33395E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63F92D-2EC4-4BBB-86DD-46C5D93A3B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{A16775A2-4027-400C-B82D-18BC41AEE9E7}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A16775A2-4027-400C-B82D-18BC41AEE9E7}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ClosedXML</t>
   </si>
@@ -108,6 +108,29 @@
     </rPh>
     <rPh sb="21" eb="22">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ProductCodeも最新化する</t>
+    <rPh sb="12" eb="14">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正したプロジェクトのバージョンも併せて変更</t>
+    <rPh sb="0" eb="2">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヘンコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -409,21 +432,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>248546</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>191258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD69E754-FCF1-3CE2-8E21-FF0AE8F27CBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B85CD1F-3F07-41DF-B05D-081812FCBDE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -439,8 +462,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="31194375"/>
+          <a:off x="685800" y="31432500"/>
           <a:ext cx="6420746" cy="5430008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>384403</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>163776</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73593C93-27A7-2BAB-C9FB-B10856A4D7AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="37861875"/>
+          <a:ext cx="24387403" cy="13260651"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -844,7 +911,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A19109-3167-4AEA-A630-E2C06EAD7D88}">
-  <dimension ref="B2:B131"/>
+  <dimension ref="B2:B159"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
@@ -860,6 +927,16 @@
     <row r="131" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B131" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B159" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
